--- a/resources/templates/standard/H3100-01.xlsx
+++ b/resources/templates/standard/H3100-01.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="36">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">번
 호</t>
@@ -802,7 +805,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -884,25 +889,25 @@
     </row>
     <row r="4" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
@@ -916,23 +921,23 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V4" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X4" s="8"/>
       <c r="Y4" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" ht="18.95" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -983,10 +988,10 @@
       <c r="U5" s="5"/>
       <c r="V5" s="7"/>
       <c r="W5" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X5" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y5" s="9"/>
     </row>
@@ -996,13 +1001,13 @@
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
@@ -1022,7 +1027,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T6" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U6" s="16"/>
       <c r="V6" s="16"/>
@@ -1034,13 +1039,13 @@
       <c r="A7" s="12"/>
       <c r="B7" s="13"/>
       <c r="C7" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="20"/>
       <c r="G7" s="20"/>
@@ -1059,7 +1064,7 @@
         <f>SUM(G7:R7)</f>
       </c>
       <c r="T7" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U7" s="21"/>
       <c r="V7" s="21"/>
@@ -1071,13 +1076,13 @@
       <c r="A8" s="12"/>
       <c r="B8" s="13"/>
       <c r="C8" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
@@ -1096,7 +1101,7 @@
         <f>SUM(G8:R8)</f>
       </c>
       <c r="T8" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U8" s="21"/>
       <c r="V8" s="21"/>
@@ -1108,13 +1113,13 @@
       <c r="A9" s="12"/>
       <c r="B9" s="13"/>
       <c r="C9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="20" t="s">
         <v>24</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>23</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
@@ -1133,7 +1138,7 @@
         <f>SUM(G9:R9)</f>
       </c>
       <c r="T9" s="20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U9" s="24"/>
       <c r="V9" s="20"/>
@@ -1145,13 +1150,13 @@
       <c r="A10" s="12"/>
       <c r="B10" s="13"/>
       <c r="C10" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" s="27"/>
       <c r="G10" s="27"/>
@@ -1171,7 +1176,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T10" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U10" s="21"/>
       <c r="V10" s="21"/>
@@ -1183,13 +1188,13 @@
       <c r="A11" s="12"/>
       <c r="B11" s="13"/>
       <c r="C11" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="28"/>
       <c r="G11" s="28"/>
@@ -1208,7 +1213,7 @@
         <f>SUM(G11:R11)</f>
       </c>
       <c r="T11" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U11" s="21"/>
       <c r="V11" s="21"/>
@@ -1220,13 +1225,13 @@
       <c r="A12" s="12"/>
       <c r="B12" s="13"/>
       <c r="C12" s="29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" s="30"/>
       <c r="G12" s="30"/>
@@ -1245,7 +1250,7 @@
         <f>SUM(G12:R12)</f>
       </c>
       <c r="T12" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U12" s="31"/>
       <c r="V12" s="31"/>
@@ -1257,13 +1262,13 @@
       <c r="A13" s="12"/>
       <c r="B13" s="13"/>
       <c r="C13" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="30"/>
@@ -1282,7 +1287,7 @@
         <f>SUM(G13:R13)</f>
       </c>
       <c r="T13" s="30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U13" s="31"/>
       <c r="V13" s="31"/>
@@ -1294,13 +1299,13 @@
       <c r="A14" s="12"/>
       <c r="B14" s="13"/>
       <c r="C14" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
@@ -1319,7 +1324,7 @@
         <f>SUM(G14:R14)</f>
       </c>
       <c r="T14" s="30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U14" s="31"/>
       <c r="V14" s="31"/>
@@ -1331,13 +1336,13 @@
       <c r="A15" s="12"/>
       <c r="B15" s="13"/>
       <c r="C15" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F15" s="35"/>
       <c r="G15" s="35"/>
@@ -1357,7 +1362,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T15" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U15" s="37"/>
       <c r="V15" s="37"/>
@@ -1371,13 +1376,13 @@
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
@@ -1397,7 +1402,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T16" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U16" s="16"/>
       <c r="V16" s="16"/>
@@ -1409,13 +1414,13 @@
       <c r="A17" s="12"/>
       <c r="B17" s="13"/>
       <c r="C17" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17" s="20"/>
       <c r="G17" s="20"/>
@@ -1434,7 +1439,7 @@
         <f>SUM(G17:R17)</f>
       </c>
       <c r="T17" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U17" s="21"/>
       <c r="V17" s="21"/>
@@ -1446,13 +1451,13 @@
       <c r="A18" s="12"/>
       <c r="B18" s="13"/>
       <c r="C18" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
@@ -1471,7 +1476,7 @@
         <f>SUM(G18:R18)</f>
       </c>
       <c r="T18" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U18" s="21"/>
       <c r="V18" s="21"/>
@@ -1483,13 +1488,13 @@
       <c r="A19" s="12"/>
       <c r="B19" s="13"/>
       <c r="C19" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>24</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>23</v>
       </c>
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
@@ -1508,7 +1513,7 @@
         <f>SUM(G19:R19)</f>
       </c>
       <c r="T19" s="20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U19" s="24"/>
       <c r="V19" s="20"/>
@@ -1520,13 +1525,13 @@
       <c r="A20" s="12"/>
       <c r="B20" s="13"/>
       <c r="C20" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F20" s="27"/>
       <c r="G20" s="27"/>
@@ -1546,7 +1551,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T20" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U20" s="21"/>
       <c r="V20" s="21"/>
@@ -1558,13 +1563,13 @@
       <c r="A21" s="12"/>
       <c r="B21" s="13"/>
       <c r="C21" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" s="28"/>
       <c r="G21" s="28"/>
@@ -1583,7 +1588,7 @@
         <f>SUM(G21:R21)</f>
       </c>
       <c r="T21" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U21" s="21"/>
       <c r="V21" s="21"/>
@@ -1595,13 +1600,13 @@
       <c r="A22" s="12"/>
       <c r="B22" s="13"/>
       <c r="C22" s="29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F22" s="30"/>
       <c r="G22" s="30"/>
@@ -1620,7 +1625,7 @@
         <f>SUM(G22:R22)</f>
       </c>
       <c r="T22" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U22" s="31"/>
       <c r="V22" s="31"/>
@@ -1632,13 +1637,13 @@
       <c r="A23" s="12"/>
       <c r="B23" s="13"/>
       <c r="C23" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23" s="30"/>
       <c r="G23" s="30"/>
@@ -1657,7 +1662,7 @@
         <f>SUM(G23:R23)</f>
       </c>
       <c r="T23" s="30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U23" s="31"/>
       <c r="V23" s="31"/>
@@ -1669,13 +1674,13 @@
       <c r="A24" s="12"/>
       <c r="B24" s="13"/>
       <c r="C24" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F24" s="30"/>
       <c r="G24" s="30"/>
@@ -1694,7 +1699,7 @@
         <f>SUM(G24:R24)</f>
       </c>
       <c r="T24" s="30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U24" s="31"/>
       <c r="V24" s="31"/>
@@ -1706,13 +1711,13 @@
       <c r="A25" s="12"/>
       <c r="B25" s="13"/>
       <c r="C25" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D25" s="35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F25" s="35"/>
       <c r="G25" s="35"/>
@@ -1732,7 +1737,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T25" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U25" s="37"/>
       <c r="V25" s="37"/>
@@ -1746,13 +1751,13 @@
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
@@ -1772,7 +1777,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T26" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U26" s="16"/>
       <c r="V26" s="16"/>
@@ -1784,13 +1789,13 @@
       <c r="A27" s="12"/>
       <c r="B27" s="13"/>
       <c r="C27" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F27" s="20"/>
       <c r="G27" s="20"/>
@@ -1809,7 +1814,7 @@
         <f>SUM(G27:R27)</f>
       </c>
       <c r="T27" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U27" s="21"/>
       <c r="V27" s="21"/>
@@ -1821,13 +1826,13 @@
       <c r="A28" s="12"/>
       <c r="B28" s="13"/>
       <c r="C28" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
@@ -1846,7 +1851,7 @@
         <f>SUM(G28:R28)</f>
       </c>
       <c r="T28" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U28" s="21"/>
       <c r="V28" s="21"/>
@@ -1858,13 +1863,13 @@
       <c r="A29" s="12"/>
       <c r="B29" s="13"/>
       <c r="C29" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="20" t="s">
         <v>24</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>23</v>
       </c>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
@@ -1883,7 +1888,7 @@
         <f>SUM(G29:R29)</f>
       </c>
       <c r="T29" s="20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U29" s="24"/>
       <c r="V29" s="20"/>
@@ -1895,13 +1900,13 @@
       <c r="A30" s="12"/>
       <c r="B30" s="13"/>
       <c r="C30" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F30" s="27"/>
       <c r="G30" s="27"/>
@@ -1921,7 +1926,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T30" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U30" s="21"/>
       <c r="V30" s="21"/>
@@ -1933,13 +1938,13 @@
       <c r="A31" s="12"/>
       <c r="B31" s="13"/>
       <c r="C31" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F31" s="28"/>
       <c r="G31" s="28"/>
@@ -1958,7 +1963,7 @@
         <f>SUM(G31:R31)</f>
       </c>
       <c r="T31" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U31" s="21"/>
       <c r="V31" s="21"/>
@@ -1970,13 +1975,13 @@
       <c r="A32" s="12"/>
       <c r="B32" s="13"/>
       <c r="C32" s="29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E32" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F32" s="30"/>
       <c r="G32" s="30"/>
@@ -1995,7 +2000,7 @@
         <f>SUM(G32:R32)</f>
       </c>
       <c r="T32" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U32" s="31"/>
       <c r="V32" s="31"/>
@@ -2007,13 +2012,13 @@
       <c r="A33" s="12"/>
       <c r="B33" s="13"/>
       <c r="C33" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E33" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F33" s="30"/>
       <c r="G33" s="30"/>
@@ -2032,7 +2037,7 @@
         <f>SUM(G33:R33)</f>
       </c>
       <c r="T33" s="30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U33" s="31"/>
       <c r="V33" s="31"/>
@@ -2044,13 +2049,13 @@
       <c r="A34" s="12"/>
       <c r="B34" s="13"/>
       <c r="C34" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F34" s="30"/>
       <c r="G34" s="30"/>
@@ -2069,7 +2074,7 @@
         <f>SUM(G34:R34)</f>
       </c>
       <c r="T34" s="30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U34" s="31"/>
       <c r="V34" s="31"/>
@@ -2081,13 +2086,13 @@
       <c r="A35" s="12"/>
       <c r="B35" s="13"/>
       <c r="C35" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E35" s="35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F35" s="35"/>
       <c r="G35" s="35"/>
@@ -2107,7 +2112,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="T35" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U35" s="37"/>
       <c r="V35" s="37"/>
